--- a/Data/RemapDrafts/NingguangRemapDraft.xlsx
+++ b/Data/RemapDrafts/NingguangRemapDraft.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FC8A31-A82C-4A21-BBFF-100D0F61B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39755A59-461C-4AE5-A14C-8CBF317C2B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{8E76B426-E694-4A38-8276-66FB6739700D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{8E76B426-E694-4A38-8276-66FB6739700D}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 - Ningguang to Orchid" sheetId="1" r:id="rId1"/>
+    <sheet name="Credits" sheetId="2" r:id="rId1"/>
+    <sheet name="V4.0 - Ningguang to Orchid" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 - Ningguang to Orchid'!$A$1:$D$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - Ningguang to Orchid'!$A$1:$D$120</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Ningguang</t>
   </si>
@@ -70,12 +71,21 @@
   <si>
     <t>Ningguang's left front dress, low tip, I don't think there is a corresponding index</t>
   </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +96,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -109,14 +135,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -459,17 +489,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DEE6BC-2598-4B1A-A048-493F5BA97683}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{32947DAD-FCAE-421C-AE04-F460DE6FBDA1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C02F1F-4996-4A24-94A0-7DAB7DB3F42E}">
   <dimension ref="A1:D120"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,7 +544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -491,7 +552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -499,7 +560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -507,7 +568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -515,7 +576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -523,7 +584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -531,7 +592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -539,7 +600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -547,7 +608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -555,7 +616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -563,7 +624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -571,7 +632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -579,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -587,7 +648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -595,7 +656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -603,7 +664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -611,7 +672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -619,7 +680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -627,7 +688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -635,7 +696,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -643,7 +704,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -651,7 +712,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -659,7 +720,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -667,7 +728,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -678,7 +739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -686,7 +747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -694,7 +755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -702,7 +763,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -710,7 +771,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -721,7 +782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -732,7 +793,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -740,7 +801,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -748,7 +809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -756,7 +817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -764,7 +825,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -772,7 +833,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -780,7 +841,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -788,7 +849,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -796,7 +857,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -804,7 +865,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -812,7 +873,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -820,7 +881,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -828,7 +889,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -836,7 +897,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -844,7 +905,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -852,7 +913,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -860,7 +921,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -868,7 +929,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -876,7 +937,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -890,7 +951,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -901,7 +962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -909,7 +970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -917,7 +978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -925,7 +986,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -933,7 +994,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -941,7 +1002,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -949,7 +1010,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -957,7 +1018,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -965,7 +1026,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -973,7 +1034,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -981,7 +1042,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -989,7 +1050,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -997,7 +1058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1005,7 +1066,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1013,7 +1074,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1021,7 +1082,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1029,7 +1090,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1037,7 +1098,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1045,7 +1106,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1053,7 +1114,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1061,7 +1122,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1069,7 +1130,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1077,7 +1138,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1085,7 +1146,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1093,7 +1154,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1101,7 +1162,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1109,7 +1170,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1117,7 +1178,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1125,7 +1186,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1133,7 +1194,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1141,7 +1202,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1149,7 +1210,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1157,7 +1218,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1165,7 +1226,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1173,7 +1234,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1181,7 +1242,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1189,7 +1250,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1197,7 +1258,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1205,7 +1266,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -1213,7 +1274,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -1221,7 +1282,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -1229,7 +1290,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -1237,7 +1298,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -1245,7 +1306,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -1253,7 +1314,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -1261,7 +1322,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -1269,7 +1330,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -1277,7 +1338,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -1285,7 +1346,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -1293,7 +1354,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -1301,7 +1362,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -1309,7 +1370,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
@@ -1317,7 +1378,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
@@ -1325,7 +1386,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>103</v>
       </c>
@@ -1333,7 +1394,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>104</v>
       </c>
@@ -1341,7 +1402,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>105</v>
       </c>
@@ -1349,7 +1410,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>106</v>
       </c>
@@ -1357,7 +1418,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>107</v>
       </c>
@@ -1365,7 +1426,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>108</v>
       </c>
@@ -1373,7 +1434,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>109</v>
       </c>
@@ -1381,7 +1442,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>110</v>
       </c>
@@ -1389,7 +1450,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>111</v>
       </c>
@@ -1397,7 +1458,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>112</v>
       </c>
@@ -1405,7 +1466,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>113</v>
       </c>
@@ -1413,7 +1474,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>114</v>
       </c>
@@ -1421,7 +1482,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>115</v>
       </c>
@@ -1429,7 +1490,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>116</v>
       </c>
@@ -1437,7 +1498,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>117</v>
       </c>
@@ -1445,7 +1506,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>118</v>
       </c>
